--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:20</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>33.48</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>112.41</v>
+        <v>112.4</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>78.93</v>
@@ -518,10 +518,10 @@
         <v>-1.15</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>42.68</v>
+        <v>42.67</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>43.82</v>
+        <v>43.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:47</t>
+    <t xml:space="preserve">2026-10-05 04:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>33.48</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>112.4</v>
+        <v>112.41</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>78.93</v>
@@ -518,7 +518,7 @@
         <v>-1.15</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>42.67</v>
+        <v>42.68</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>43.83</v>
